--- a/ocm_project_summary.xlsx
+++ b/ocm_project_summary.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1. Project Journey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2. Dataset Stats" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3. Method Comparison" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4. OOD Robustness" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5. Element Usage" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="6. SHAP Analysis" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7. Residual Analysis" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="8. Methodological Notes" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="9. Next Steps" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Project Journey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Dataset Stats" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Method Comparison" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. OOD Robustness" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Element Usage" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. SHAP Analysis" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. Residual Analysis" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. Methodological Notes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. Next Steps" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -882,7 +882,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>BEST RESULT: RMSE 1.907% (−10.6%). OOD test: 6.53→3.60 (−45%).</t>
+          <t>BEST RESULT: RMSE 1.907% (−10.6%), 10/10 seeds p&lt;1e-14, held-out 2.097→1.892. OOD (leak-free): 6.53→6.77 (≈baseline); old 6.53→3.60 was leakage.</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -1644,7 +1644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1707,80 +1707,102 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Model trained only on impregnation data fails badly on other prep methods</t>
+          <t>Model trained only on impregnation data; reference point</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Naive concatenation</t>
+          <t>DRST-filtered + raw labels</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>−4.9%</t>
+          <t>−6.4%</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Small gain but still poor — label shift confuses the model</t>
+          <t>Leak-free; small honest gain on unseen prep methods</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>DRST (τ=0.30)</t>
+          <t>Full impreg-lit + raw labels</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>−24.2%</t>
+          <t>−7.4%</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Better — filtered literature provides some generalization signal</t>
+          <t>Leak-free; best honest OOD — literature-scale prior helps most</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Two-stage fine-tuning ★</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>−45.0% ✅</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>BEST — Stage 1 literature prior gives model a chemistry map of unseen space</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Two-stage PFT (DRST + QN)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>6.77</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>+3.7%</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Leak-free; QN calibrates to lab scale → slightly worse OOD (the trade-off)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>Key insight: OOD improvement (−45%) is larger than in-distribution improvement (−10.6%). This confirms the two-stage method genuinely learns transferable chemistry knowledge, not just in-distribution memorization.</t>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>OLD 'two-stage' (3.60, leaky)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>−44.6% ✗</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>REPRODUCED ONLY WITH LEAKAGE — prior trained on the OOD test rows/labels</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>Correction &amp; key insight: the old −45% OOD (3.60) was DATA LEAKAGE — the Stage-1 prior was trained on the OOD test rows and their labels (reproduced here as 3.62). Leak-free, OOD gains are modest (~6.0–6.8). Quantile normalisation (QN) improves in-distribution accuracy but slightly worsens OOD — a deliberate trade-off. The strong, honest result is in-distribution: −10.6%, 10/10 seeds, p&lt;1e-14, held-out.</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1810,7 @@
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ocm_project_summary.xlsx
+++ b/ocm_project_summary.xlsx
@@ -180,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -233,10 +233,13 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -782,7 +785,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>RMSE WORSENED to 2.248% (+5.4%). Label shift and covariate shift caused contradictory gradients.</t>
+          <t>RMSE WORSENED to 2.241% (+5.1%). Label shift and covariate shift caused contradictory gradients.</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -807,7 +810,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>RMSE improved to 2.019% (−5.3%). Only chemically similar literature enters training.</t>
+          <t>RMSE ~2.18% (tau=0.30) / best 2.127% over the full sweep = no gain over baseline. Filtering removes foreign chemistry but not the label shift.</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -832,7 +835,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>RMSE improved to 2.035% (−4.6%). Soft alternative to hard DRST filter. Correlation with DRST scores r=0.792.</t>
+          <t>RMSE 2.261% (+6.0%, worse). Soft alternative to hard DRST filter (r=0.792 with DRST); still injects biased literature labels, so it also fails to beat baseline.</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1488,12 +1491,12 @@
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>2.248</t>
+          <t>2.241</t>
         </is>
       </c>
       <c r="E4" s="17" t="inlineStr">
         <is>
-          <t>+5.4% ❌</t>
+          <t>+5.1% ❌</t>
         </is>
       </c>
       <c r="F4" s="16" t="inlineStr">
@@ -1518,17 +1521,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2.019</t>
+          <t>2.181</t>
         </is>
       </c>
       <c r="E5" s="18" t="inlineStr">
         <is>
-          <t>−5.3% ✓</t>
+          <t>+2.3% ❌</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Good hard filter; interpretable threshold</t>
+          <t>Filtering alone does not beat baseline (best over sweep 2.127)</t>
         </is>
       </c>
     </row>
@@ -1548,17 +1551,17 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>2.035</t>
+          <t>2.261</t>
         </is>
       </c>
       <c r="E6" s="19" t="inlineStr">
         <is>
-          <t>−4.6% ✓</t>
+          <t>+6.0% ❌</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Soft alternative to DRST; correlated (r=0.792) but slower</t>
+          <t>Soft alternative to DRST; correlated (r=0.792) but also worse than baseline</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1584,7 @@
           <t>2.044</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>−4.2% ✓</t>
         </is>
@@ -1611,7 +1614,7 @@
           <t>1.907</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>−10.6% ✅</t>
         </is>
@@ -1623,7 +1626,7 @@
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>CV protocol: 5-fold split applied ONLY to internal 89k samples. Literature always in training pool, never in validation folds. This is called asymmetric cross-validation.</t>
         </is>
@@ -1661,7 +1664,7 @@
       </c>
     </row>
     <row r="2" ht="38" customHeight="1">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>OOD test set: 2,139 literature samples from NON-Impregnation preparation methods (e.g. sol-gel, coprecipitation, combustion). These samples were NEVER used in any training or validation fold. This is a true held-out generalization test.</t>
         </is>
@@ -1800,7 +1803,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>Correction &amp; key insight: the old −45% OOD (3.60) was DATA LEAKAGE — the Stage-1 prior was trained on the OOD test rows and their labels (reproduced here as 3.62). Leak-free, OOD gains are modest (~6.0–6.8). Quantile normalisation (QN) improves in-distribution accuracy but slightly worsens OOD — a deliberate trade-off. The strong, honest result is in-distribution: −10.6%, 10/10 seeds, p&lt;1e-14, held-out.</t>
         </is>
@@ -1889,140 +1892,140 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Dominates our data; rare in literature</t>
+          <t>Dominates lab data; rare in literature</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>~3</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>31.8</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>+28.8</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="24" t="inlineStr">
         <is>
           <t>Literature-dominant — silica supports common</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>Na</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>~4</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>30.1</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t>+26.1</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t>Literature-dominant — Na promoters widely studied</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>Mn</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>~5</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>28.4</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>+23.4</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>Literature-dominant — Mn/Mg catalysts common</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>La</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>~8</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>~22</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t>+14</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t>More common in literature</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Ce</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>~6</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>~18</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>+12</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="24" t="inlineStr">
         <is>
           <t>Ceria more common in literature</t>
         </is>
@@ -2083,54 +2086,54 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>Mg</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>~4</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>~20</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>+16</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>Magnesia supports more common in literature</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>Li</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>~3</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>~15</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="24" t="inlineStr">
         <is>
           <t>+12</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="24" t="inlineStr">
         <is>
           <t>Alkali promoters — literature-heavier</t>
         </is>
@@ -2191,7 +2194,7 @@
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>Important correction: Sr (strontium) appears in BOTH datasets (ours 7.5%, lit 11.1%). It is NOT exclusive to literature. Always verify element claims against actual data before stating them in a presentation.</t>
         </is>
@@ -2452,7 +2455,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>High Na loadings sinter the catalyst surface in our data</t>
+          <t>High Na loadings sinter the catalyst surface in lab data</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2510,7 @@
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>Method: shap.TreeExplainer on the final LightGBM model. 3,000 samples randomly drawn from the full dataset. Beeswarm plot shows each sample's SHAP value per feature. Direction: positive SHAP = feature value pushes prediction higher.</t>
         </is>
@@ -2546,7 +2549,7 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Residual = predicted Y(C2) − actual Y(C2). Negative mean residual means the model systematically UNDER-predicts that range.</t>
         </is>
@@ -2580,54 +2583,54 @@
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>0 – 3%</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>1.427</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>≈ 0.0</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>~35,000</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
-        <is>
-          <t>Well-calibrated — bulk of our data falls here</t>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>Well-calibrated — bulk of lab data falls here</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>3 – 6%</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>1.476</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>≈ 0.0</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t>~30,000</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t>Well-calibrated — good coverage in training</t>
         </is>
@@ -2688,27 +2691,27 @@
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>&gt; 15%</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>4.695</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>−4.159</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>~2,000</t>
         </is>
       </c>
-      <c r="E8" s="24" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>CEILING EFFECT: systematic −4.2% bias; missing GHSV/CH₄:O₂</t>
         </is>
@@ -2832,7 +2835,7 @@
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>Adding GHSV and CH₄/O₂ ratio is the single highest-impact improvement available. Expected to reduce Y&gt;15% RMSE from 4.695% to ~2.5% and eliminate the −4.2% mean bias.</t>
         </is>
@@ -2916,22 +2919,22 @@
       </c>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>Stage 1 Training Data</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>Stage 1 XGBoost trained on (DRST-filtered literature + train_fold internal samples).</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="26" t="inlineStr">
         <is>
           <t>In-sample predictions generated for train_fold — Stage 2 trains on near-perfect priors. Slight calibration mismatch at deployment.</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>Train Stage 1 on literature only → all internal priors become out-of-sample. One-line fix, no performance loss expected.</t>
         </is>
